--- a/fhir/finnish-smart/StructureDefinition-fi-smart-immunization.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-immunization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc2</t>
+    <t>2.0.0-rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-11T17:07:13+03:00</t>
+    <t>2025-06-01T15:36:45+03:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/finnish-smart/StructureDefinition-fi-smart-immunization.xlsx
+++ b/fhir/finnish-smart/StructureDefinition-fi-smart-immunization.xlsx
@@ -9,9 +9,6 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$121</definedName>
-  </definedNames>
 </workbook>
 </file>
 
@@ -33,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-rc3</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-01T15:36:45+03:00</t>
+    <t>2025-10-26T13:24:16+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1931,21 +1928,6 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor indexed="22"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color indexed="22"/>
-        <i val="true"/>
-      </font>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -2289,7 +2271,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" hidden="true">
+    <row r="2">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -2404,7 +2386,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>88</v>
       </c>
@@ -2521,7 +2503,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" hidden="true">
+    <row r="4">
       <c r="A4" t="s" s="2">
         <v>96</v>
       </c>
@@ -2636,7 +2618,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>102</v>
       </c>
@@ -2753,7 +2735,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="6" hidden="true">
+    <row r="6">
       <c r="A6" t="s" s="2">
         <v>108</v>
       </c>
@@ -2870,7 +2852,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>117</v>
       </c>
@@ -2987,7 +2969,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="8" hidden="true">
+    <row r="8">
       <c r="A8" t="s" s="2">
         <v>125</v>
       </c>
@@ -3104,7 +3086,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>133</v>
       </c>
@@ -3217,7 +3199,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>141</v>
       </c>
@@ -3334,7 +3316,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>146</v>
       </c>
@@ -3453,7 +3435,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" hidden="true">
+    <row r="12">
       <c r="A12" t="s" s="2">
         <v>153</v>
       </c>
@@ -3568,7 +3550,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
         <v>161</v>
       </c>
@@ -3587,7 +3569,7 @@
         <v>89</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>90</v>
@@ -3685,7 +3667,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>171</v>
       </c>
@@ -3704,7 +3686,7 @@
         <v>89</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>78</v>
@@ -3802,7 +3784,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>181</v>
       </c>
@@ -3821,7 +3803,7 @@
         <v>89</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>78</v>
@@ -3917,7 +3899,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
         <v>191</v>
       </c>
@@ -4032,7 +4014,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
         <v>197</v>
       </c>
@@ -4149,7 +4131,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>202</v>
       </c>
@@ -4266,7 +4248,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>212</v>
       </c>
@@ -4387,7 +4369,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>215</v>
       </c>
@@ -4502,7 +4484,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>217</v>
       </c>
@@ -4619,7 +4601,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>219</v>
       </c>
@@ -4738,7 +4720,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>229</v>
       </c>
@@ -4855,7 +4837,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>237</v>
       </c>
@@ -4972,7 +4954,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>245</v>
       </c>
@@ -5089,7 +5071,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>253</v>
       </c>
@@ -5208,7 +5190,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>263</v>
       </c>
@@ -5329,7 +5311,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>265</v>
       </c>
@@ -5444,7 +5426,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>266</v>
       </c>
@@ -5561,7 +5543,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>267</v>
       </c>
@@ -5680,7 +5662,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>269</v>
       </c>
@@ -5797,7 +5779,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="32" hidden="true">
+    <row r="32">
       <c r="A32" t="s" s="2">
         <v>270</v>
       </c>
@@ -5914,7 +5896,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>271</v>
       </c>
@@ -6031,7 +6013,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>272</v>
       </c>
@@ -6150,7 +6132,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>273</v>
       </c>
@@ -6269,7 +6251,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
         <v>281</v>
       </c>
@@ -6288,7 +6270,7 @@
         <v>89</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>78</v>
@@ -6384,7 +6366,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>289</v>
       </c>
@@ -6499,7 +6481,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>297</v>
       </c>
@@ -6518,7 +6500,7 @@
         <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -6616,7 +6598,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>307</v>
       </c>
@@ -6731,7 +6713,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>313</v>
       </c>
@@ -6848,7 +6830,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>320</v>
       </c>
@@ -6965,7 +6947,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>327</v>
       </c>
@@ -7080,7 +7062,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>335</v>
       </c>
@@ -7195,7 +7177,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>342</v>
       </c>
@@ -7310,7 +7292,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>348</v>
       </c>
@@ -7425,7 +7407,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" hidden="true">
+    <row r="46">
       <c r="A46" t="s" s="2">
         <v>354</v>
       </c>
@@ -7540,7 +7522,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>362</v>
       </c>
@@ -7655,7 +7637,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
         <v>363</v>
       </c>
@@ -7772,7 +7754,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" hidden="true">
+    <row r="49">
       <c r="A49" t="s" s="2">
         <v>364</v>
       </c>
@@ -7889,7 +7871,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
         <v>365</v>
       </c>
@@ -8010,7 +7992,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
         <v>367</v>
       </c>
@@ -8125,7 +8107,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>369</v>
       </c>
@@ -8242,7 +8224,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>371</v>
       </c>
@@ -8361,7 +8343,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
         <v>374</v>
       </c>
@@ -8478,7 +8460,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>376</v>
       </c>
@@ -8595,7 +8577,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>378</v>
       </c>
@@ -8712,7 +8694,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
         <v>380</v>
       </c>
@@ -8831,7 +8813,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>382</v>
       </c>
@@ -8950,7 +8932,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>384</v>
       </c>
@@ -9065,7 +9047,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
         <v>392</v>
       </c>
@@ -9180,7 +9162,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>393</v>
       </c>
@@ -9297,7 +9279,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>394</v>
       </c>
@@ -9414,7 +9396,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
         <v>395</v>
       </c>
@@ -9535,7 +9517,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>397</v>
       </c>
@@ -9650,7 +9632,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>399</v>
       </c>
@@ -9767,7 +9749,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>401</v>
       </c>
@@ -9886,7 +9868,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>404</v>
       </c>
@@ -10003,7 +9985,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
         <v>406</v>
       </c>
@@ -10120,7 +10102,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="69" hidden="true">
+    <row r="69">
       <c r="A69" t="s" s="2">
         <v>408</v>
       </c>
@@ -10237,7 +10219,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>410</v>
       </c>
@@ -10356,7 +10338,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="71" hidden="true">
+    <row r="71">
       <c r="A71" t="s" s="2">
         <v>412</v>
       </c>
@@ -10475,7 +10457,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="72" hidden="true">
+    <row r="72">
       <c r="A72" t="s" s="2">
         <v>413</v>
       </c>
@@ -10590,7 +10572,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="73" hidden="true">
+    <row r="73">
       <c r="A73" t="s" s="2">
         <v>419</v>
       </c>
@@ -10705,7 +10687,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="74" hidden="true">
+    <row r="74">
       <c r="A74" t="s" s="2">
         <v>426</v>
       </c>
@@ -10820,7 +10802,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>427</v>
       </c>
@@ -10937,7 +10919,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>428</v>
       </c>
@@ -11056,7 +11038,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="77" hidden="true">
+    <row r="77">
       <c r="A77" t="s" s="2">
         <v>433</v>
       </c>
@@ -11171,7 +11153,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>441</v>
       </c>
@@ -11288,7 +11270,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>449</v>
       </c>
@@ -11403,7 +11385,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="80" hidden="true">
+    <row r="80">
       <c r="A80" t="s" s="2">
         <v>456</v>
       </c>
@@ -11518,7 +11500,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="81" hidden="true">
+    <row r="81">
       <c r="A81" t="s" s="2">
         <v>463</v>
       </c>
@@ -11633,7 +11615,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>467</v>
       </c>
@@ -11752,7 +11734,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>473</v>
       </c>
@@ -11867,7 +11849,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>478</v>
       </c>
@@ -11982,7 +11964,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>482</v>
       </c>
@@ -12097,7 +12079,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>483</v>
       </c>
@@ -12214,7 +12196,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="87" hidden="true">
+    <row r="87">
       <c r="A87" t="s" s="2">
         <v>484</v>
       </c>
@@ -12333,7 +12315,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>485</v>
       </c>
@@ -12448,7 +12430,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="89" hidden="true">
+    <row r="89">
       <c r="A89" t="s" s="2">
         <v>489</v>
       </c>
@@ -12563,7 +12545,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
         <v>492</v>
       </c>
@@ -12678,7 +12660,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>496</v>
       </c>
@@ -12793,7 +12775,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
         <v>500</v>
       </c>
@@ -12908,7 +12890,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" hidden="true">
+    <row r="93">
       <c r="A93" t="s" s="2">
         <v>506</v>
       </c>
@@ -13023,7 +13005,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="94" hidden="true">
+    <row r="94">
       <c r="A94" t="s" s="2">
         <v>511</v>
       </c>
@@ -13140,7 +13122,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>517</v>
       </c>
@@ -13255,7 +13237,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="96" hidden="true">
+    <row r="96">
       <c r="A96" t="s" s="2">
         <v>518</v>
       </c>
@@ -13372,7 +13354,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>519</v>
       </c>
@@ -13491,7 +13473,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>520</v>
       </c>
@@ -13606,7 +13588,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>524</v>
       </c>
@@ -13721,7 +13703,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="100" hidden="true">
+    <row r="100">
       <c r="A100" t="s" s="2">
         <v>530</v>
       </c>
@@ -13836,7 +13818,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>535</v>
       </c>
@@ -13951,7 +13933,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>538</v>
       </c>
@@ -14066,7 +14048,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>539</v>
       </c>
@@ -14183,7 +14165,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>540</v>
       </c>
@@ -14302,7 +14284,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
         <v>541</v>
       </c>
@@ -14417,7 +14399,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="106" hidden="true">
+    <row r="106">
       <c r="A106" t="s" s="2">
         <v>544</v>
       </c>
@@ -14532,7 +14514,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>547</v>
       </c>
@@ -14647,7 +14629,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="108" hidden="true">
+    <row r="108">
       <c r="A108" t="s" s="2">
         <v>552</v>
       </c>
@@ -14762,7 +14744,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="109" hidden="true">
+    <row r="109">
       <c r="A109" t="s" s="2">
         <v>553</v>
       </c>
@@ -14879,7 +14861,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
         <v>554</v>
       </c>
@@ -14996,7 +14978,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>556</v>
       </c>
@@ -15117,7 +15099,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="112" hidden="true">
+    <row r="112">
       <c r="A112" t="s" s="2">
         <v>558</v>
       </c>
@@ -15232,7 +15214,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
         <v>560</v>
       </c>
@@ -15349,7 +15331,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
         <v>562</v>
       </c>
@@ -15468,7 +15450,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>565</v>
       </c>
@@ -15585,7 +15567,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="116" hidden="true">
+    <row r="116">
       <c r="A116" t="s" s="2">
         <v>567</v>
       </c>
@@ -15702,7 +15684,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>569</v>
       </c>
@@ -15819,7 +15801,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>571</v>
       </c>
@@ -15938,7 +15920,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>573</v>
       </c>
@@ -16057,7 +16039,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>574</v>
       </c>
@@ -16174,7 +16156,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>579</v>
       </c>
@@ -16292,24 +16274,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO121">
-    <filterColumn colId="6">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="26">
-      <filters blank="true"/>
-    </filterColumn>
-  </autoFilter>
-  <conditionalFormatting sqref="A2:AI120">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$G2&lt;&gt;"Y"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$Q2&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>